--- a/jogos_2025-02-06.xlsx
+++ b/jogos_2025-02-06.xlsx
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.29</v>
+        <v>1.72</v>
       </c>
       <c r="M5" t="n">
-        <v>2.64</v>
+        <v>3.41</v>
       </c>
       <c r="N5" t="n">
-        <v>2.59</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="T5" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="X5" t="n">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.21</v>
+        <v>2.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AA5" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['11', '81']</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['40']</t>
+          <t>['23', '51']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.33</v>
+        <v>2.05</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45694.45833333334</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>CSM Iaşi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.72</v>
+        <v>2.47</v>
       </c>
       <c r="M6" t="n">
-        <v>3.41</v>
+        <v>3.07</v>
       </c>
       <c r="N6" t="n">
-        <v>5.1</v>
+        <v>2.95</v>
       </c>
       <c r="O6" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X6" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['23', '51']</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.05</v>
+        <v>1.49</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45694.45833333334</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CSM Iaşi</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.47</v>
+        <v>3.29</v>
       </c>
       <c r="M7" t="n">
-        <v>3.07</v>
+        <v>2.64</v>
       </c>
       <c r="N7" t="n">
-        <v>2.95</v>
+        <v>2.59</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="W7" t="n">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="X7" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.25</v>
+        <v>3.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.91</v>
+        <v>2.55</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '81']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['40']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45694.45833333334</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Basel</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.63</v>
+        <v>1.75</v>
       </c>
       <c r="M15" t="n">
-        <v>3.62</v>
+        <v>3.94</v>
       </c>
       <c r="N15" t="n">
-        <v>1.93</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.6</v>
+        <v>2.15</v>
       </c>
       <c r="P15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="U15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X15" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['4', '57']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>2.6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['63', '80']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45694.6875</v>
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Basel</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>2</v>
       </c>
-      <c r="H16" t="n">
-        <v>1</v>
-      </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.75</v>
+        <v>3.63</v>
       </c>
       <c r="M16" t="n">
-        <v>3.94</v>
+        <v>3.62</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>1.93</v>
       </c>
       <c r="O16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.15</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="T16" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="Z16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['63', '80']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI16" t="n">
         <v>2.25</v>
       </c>
-      <c r="AA16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['4', '57']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['1']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>2.6</v>
+        <v>1.73</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45694.6875</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,81 +2578,81 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="O17" t="n">
         <v>3</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M17" t="n">
+      <c r="P17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3.6</v>
       </c>
-      <c r="N17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>4</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.63</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T17" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W17" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X17" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC17" t="n">
         <v>1.67</v>
@@ -2662,25 +2662,25 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['59', '68', '89']</t>
+          <t>['11', '37', '54', '59', '90+4']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+4', '90+3']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45694.69791666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,81 +2707,81 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.99</v>
-      </c>
       <c r="O18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.4</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.35</v>
       </c>
       <c r="AC18" t="n">
         <v>1.67</v>
@@ -2791,25 +2791,25 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['11', '37', '54', '59', '90+4']</t>
+          <t>['59', '68', '89']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['45+4', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45694.69791666666</v>
